--- a/data/estacionamento_bh.xlsx
+++ b/data/estacionamento_bh.xlsx
@@ -8,19 +8,34 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patrick\Desktop\Curso em Vídeo HTML5 e CSS3\exercicios\dashboard-estacionamento-bh\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AE154E0F-EEE4-43C1-8545-08CBFB706967}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A68FFA-532A-414E-810D-5C9128DDABBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8316B71B-52D7-42FF-8630-4572AF6B553D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{8316B71B-52D7-42FF-8630-4572AF6B553D}"/>
   </bookViews>
   <sheets>
-    <sheet name="Dados" sheetId="1" r:id="rId1"/>
+    <sheet name="01_Dados" sheetId="1" r:id="rId1"/>
+    <sheet name="02_Tabela_Vagas" sheetId="2" r:id="rId2"/>
+    <sheet name="03_Tabela_Uso" sheetId="3" r:id="rId3"/>
+    <sheet name="04__Dashboard" sheetId="6" r:id="rId4"/>
+    <sheet name="assets" sheetId="7" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Dados!$A$1:$A$21</definedName>
-    <definedName name="estacionamento_motofrete_analitico" localSheetId="0">Dados!$A$1:$A$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'01_Dados'!$A$1:$A$21</definedName>
+    <definedName name="SegmentaçãodeDados_BAIRRO">#N/A</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <pivotCaches>
+    <pivotCache cacheId="1" r:id="rId6"/>
+  </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId7"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -28,20 +43,8 @@
 </workbook>
 </file>
 
-<file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
-<connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16">
-  <connection id="1" xr16:uid="{93FB0076-1E30-4A56-9BB7-FCE6E71D2A43}" name="estacionamento_motofrete_analitico" type="6" refreshedVersion="8" background="1" saveData="1">
-    <textPr sourceFile="C:\Users\Patrick\Desktop\Curso em Vídeo HTML5 e CSS3\exercicios\dashboard-estacionamento-bh\data\estacionamento_motofrete_analitico.csv" decimal="," thousands=".">
-      <textFields>
-        <textField/>
-      </textFields>
-    </textPr>
-  </connection>
-</connections>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="32">
   <si>
     <t>BAIRRO</t>
   </si>
@@ -67,9 +70,6 @@
     <t>SERRA VERDE</t>
   </si>
   <si>
-    <t>SANTA EFIGÃŠNIA</t>
-  </si>
-  <si>
     <t>BARRO PRETO</t>
   </si>
   <si>
@@ -80,9 +80,6 @@
   </si>
   <si>
     <t>BOA VIAGEM</t>
-  </si>
-  <si>
-    <t>FUNCIONÃRIOS</t>
   </si>
   <si>
     <t>BARREIRO</t>
@@ -97,12 +94,6 @@
     <t>BURITIS</t>
   </si>
   <si>
-    <t>CAIÃ‡ARAS</t>
-  </si>
-  <si>
-    <t>SANTA LÃšCIA</t>
-  </si>
-  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
@@ -112,13 +103,43 @@
     <t>FLORESTA</t>
   </si>
   <si>
-    <t>SÃƒO PEDRO</t>
-  </si>
-  <si>
     <t>ALPES</t>
   </si>
   <si>
     <t>VENDA NOVA</t>
+  </si>
+  <si>
+    <t>Rótulos de Linha</t>
+  </si>
+  <si>
+    <t>Total Geral</t>
+  </si>
+  <si>
+    <t>Soma de TOTAL_VAGAS_ROTATIVAS</t>
+  </si>
+  <si>
+    <t>CAIÇARAS</t>
+  </si>
+  <si>
+    <t>FUNCIONÁRIOS</t>
+  </si>
+  <si>
+    <t>SÃO PEDRO</t>
+  </si>
+  <si>
+    <t>SANTA EFIGÊNIA</t>
+  </si>
+  <si>
+    <t>SANTA LÚCIA</t>
+  </si>
+  <si>
+    <t>Total de Vagas Rotativas</t>
+  </si>
+  <si>
+    <t>Soma de TOTAL_REGISTROS</t>
+  </si>
+  <si>
+    <t>soma_vagas_ficica+rotativa</t>
   </si>
 </sst>
 </file>
@@ -134,12 +155,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -154,16 +181,48 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="8">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -176,8 +235,3282 @@
 </styleSheet>
 </file>
 
-<file path=xl/queryTables/queryTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<queryTable xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr16="http://schemas.microsoft.com/office/spreadsheetml/2017/revision16" mc:Ignorable="xr16" name="estacionamento_motofrete_analitico" connectionId="1" xr16:uid="{8DB8683E-9033-461F-809E-EE4580DB8DCD}" autoFormatId="16" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="0"/>
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[estacionamento_bh.xlsx]02_Tabela_Vagas!Tabela dinâmica1</c:name>
+    <c:fmtId val="2"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst>
+                <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                  <a:prstClr val="black">
+                    <a:alpha val="40000"/>
+                  </a:prstClr>
+                </a:outerShdw>
+              </a:effectLst>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="diamond"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'02_Tabela_Vagas'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="lt1">
+                        <a:lumMod val="85000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525">
+                      <a:solidFill>
+                        <a:schemeClr val="lt1">
+                          <a:lumMod val="95000"/>
+                          <a:alpha val="54000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'02_Tabela_Vagas'!$A$4:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SERRA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'02_Tabela_Vagas'!$B$4:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>10995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-600E-44CB-AD39-AB1D17BBFDD6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="115"/>
+        <c:overlap val="-20"/>
+        <c:axId val="1865842352"/>
+        <c:axId val="1865826032"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1865842352"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1865826032"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1865826032"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1865842352"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneSeries val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[estacionamento_bh.xlsx]03_Tabela_Uso!Tabela dinâmica2</c:name>
+    <c:fmtId val="3"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:autoTitleDeleted val="1"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="diamond"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:gradFill rotWithShape="1">
+            <a:gsLst>
+              <a:gs pos="0">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="103000"/>
+                  <a:lumMod val="102000"/>
+                  <a:tint val="94000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="50000">
+                <a:schemeClr val="accent1">
+                  <a:satMod val="110000"/>
+                  <a:lumMod val="100000"/>
+                  <a:shade val="100000"/>
+                </a:schemeClr>
+              </a:gs>
+              <a:gs pos="100000">
+                <a:schemeClr val="accent1">
+                  <a:lumMod val="99000"/>
+                  <a:satMod val="120000"/>
+                  <a:shade val="78000"/>
+                </a:schemeClr>
+              </a:gs>
+            </a:gsLst>
+            <a:lin ang="5400000" scaled="0"/>
+          </a:gradFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="square"/>
+          <c:size val="5"/>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln w="9525">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="lt1">
+                      <a:lumMod val="85000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout>
+        <c:manualLayout>
+          <c:layoutTarget val="inner"/>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.26526463719594107"/>
+          <c:y val="0.24280272056966593"/>
+          <c:w val="0.66586397172794343"/>
+          <c:h val="0.68025445469386536"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:barChart>
+        <c:barDir val="bar"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'03_Tabela_Uso'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Soma de TOTAL_REGISTROS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent1">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'03_Tabela_Uso'!$A$4:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SERRA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'03_Tabela_Uso'!$B$4:$B$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>182</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-2744-416E-AC11-DEAA39AFF730}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'03_Tabela_Uso'!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Soma de TOTAL_VAGAS_ROTATIVAS</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:gradFill rotWithShape="1">
+              <a:gsLst>
+                <a:gs pos="0">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="103000"/>
+                    <a:lumMod val="102000"/>
+                    <a:tint val="94000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="50000">
+                  <a:schemeClr val="accent2">
+                    <a:satMod val="110000"/>
+                    <a:lumMod val="100000"/>
+                    <a:shade val="100000"/>
+                  </a:schemeClr>
+                </a:gs>
+                <a:gs pos="100000">
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="99000"/>
+                    <a:satMod val="120000"/>
+                    <a:shade val="78000"/>
+                  </a:schemeClr>
+                </a:gs>
+              </a:gsLst>
+              <a:lin ang="5400000" scaled="0"/>
+            </a:gradFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst>
+              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+                <a:srgbClr val="000000">
+                  <a:alpha val="63000"/>
+                </a:srgbClr>
+              </a:outerShdw>
+            </a:effectLst>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'03_Tabela_Uso'!$A$4:$A$5</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>SERRA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'03_Tabela_Uso'!$C$4:$C$5</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>10995</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-2744-416E-AC11-DEAA39AFF730}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="115"/>
+        <c:overlap val="-20"/>
+        <c:axId val="1866881904"/>
+        <c:axId val="1866883344"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="1866881904"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="lt1">
+                <a:lumMod val="95000"/>
+                <a:alpha val="54000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1866883344"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1866883344"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="95000"/>
+                  <a:alpha val="10000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="lt1">
+                    <a:lumMod val="85000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1866881904"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="t"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.17970233834407062"/>
+          <c:y val="2.0942408376963352E-2"/>
+          <c:w val="0.59135260081126217"/>
+          <c:h val="0.14048948069972927"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1">
+                  <a:lumMod val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:gradFill flip="none" rotWithShape="1">
+      <a:gsLst>
+        <a:gs pos="0">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:gs>
+        <a:gs pos="100000">
+          <a:schemeClr val="dk1">
+            <a:lumMod val="85000"/>
+            <a:lumOff val="15000"/>
+          </a:schemeClr>
+        </a:gs>
+      </a:gsLst>
+      <a:path path="circle">
+        <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+      </a:path>
+      <a:tileRect/>
+    </a:gradFill>
+    <a:ln>
+      <a:noFill/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="222">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="222">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200" cap="all"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:gradFill flip="none" rotWithShape="1">
+        <a:gsLst>
+          <a:gs pos="0">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="65000"/>
+              <a:lumOff val="35000"/>
+            </a:schemeClr>
+          </a:gs>
+          <a:gs pos="100000">
+            <a:schemeClr val="dk1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:gs>
+        </a:gsLst>
+        <a:path path="circle">
+          <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+        </a:path>
+        <a:tileRect/>
+      </a:gradFill>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="34925" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="3"/>
+    <cs:effectRef idx="3"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="10000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="5000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:prstDash val="dash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="95000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1600" b="1" kern="1200" spc="100" baseline="0">
+      <a:effectLst>
+        <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+          <a:prstClr val="black">
+            <a:alpha val="40000"/>
+          </a:prstClr>
+        </a:outerShdw>
+      </a:effectLst>
+    </cs:defRPr>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1">
+            <a:lumMod val="95000"/>
+            <a:alpha val="54000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="lt1">
+        <a:lumMod val="85000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>600076</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FDCCBC23-3A2A-40D9-A150-CDD696B09CA0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3552C30F-56C5-4DDC-A8B7-F079C7BAFE30}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="7" name="BAIRRO">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A13D607-2F65-3E4A-3C4C-B2ED1CC76DCD}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="BAIRRO"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="8372475" y="419100"/>
+              <a:ext cx="1828800" cy="3600450"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Esta forma representa uma segmentação de dados. Segmentações de dados têm suporte no Excel 2010 ou versões posteriores.
+\Se a forma tiver sido modificada em uma versão anterior do Excel, ou se a pasta de trabalho tiver sido salva no Excel 2003 ou versões anteriores, a segmentação de dados não poderá ser usada.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>584488</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>92652</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>502227</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>165861</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Gráfico 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CDDADAA-B401-4677-BCC3-D68AAFB49C00}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId4"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3615170" y="473652"/>
+          <a:ext cx="523875" cy="644709"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>243321</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>80530</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>161059</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>153739</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Gráfico 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ABF9DACF-8F4C-45EC-A2E3-482C8694111F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId4"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7516957" y="461530"/>
+          <a:ext cx="523875" cy="644709"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5121" name="AutoShape 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1BD80F25-4DA1-F304-EDD7-1C0A67FF7B47}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="5122" name="AutoShape 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED41B631-8783-878D-3883-7F339224E942}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="571500"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>19051</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>433778</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>19051</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0C1D99F-2E90-0D2E-F70C-864F80594776}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId2"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2076450" y="781051"/>
+          <a:ext cx="1405328" cy="1714500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Patrick Helmer" refreshedDate="46125.959997453705" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="20" xr:uid="{3E6E6604-D3A3-4F0D-8B36-13BA7F1DE08A}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:E21" sheet="01_Dados"/>
+  </cacheSource>
+  <cacheFields count="5">
+    <cacheField name="BAIRRO" numFmtId="0">
+      <sharedItems count="25">
+        <s v="CENTRO"/>
+        <s v="SERRA VERDE"/>
+        <s v="SANTA EFIGÊNIA"/>
+        <s v="BARRO PRETO"/>
+        <s v="SAVASSI"/>
+        <s v="SANTO AGOSTINHO"/>
+        <s v="BOA VIAGEM"/>
+        <s v="FUNCIONÁRIOS"/>
+        <s v="BARREIRO"/>
+        <s v="SERRA"/>
+        <s v="LOURDES"/>
+        <s v="BURITIS"/>
+        <s v="CAIÇARAS"/>
+        <s v="SANTA LÚCIA"/>
+        <s v="GUTIERREZ"/>
+        <s v="BELVEDERE"/>
+        <s v="FLORESTA"/>
+        <s v="SÃO PEDRO"/>
+        <s v="ALPES"/>
+        <s v="VENDA NOVA"/>
+        <s v="SANTA EFIGÃŠNIA" u="1"/>
+        <s v="FUNCIONÃRIOS" u="1"/>
+        <s v="CAIÃ‡ARAS" u="1"/>
+        <s v="SANTA LÃšCIA" u="1"/>
+        <s v="SÃƒO PEDRO" u="1"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="TIPO_ESTACIONAMENTO" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="TOTAL_VAGAS_FISICAS" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="432" maxValue="14846"/>
+    </cacheField>
+    <cacheField name="TOTAL_VAGAS_ROTATIVAS" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3240" maxValue="111345"/>
+    </cacheField>
+    <cacheField name="TOTAL_REGISTROS" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="54" maxValue="1064"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition pivotCacheId="262922932"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="20">
+  <r>
+    <x v="0"/>
+    <s v="ROTATIVO"/>
+    <n v="14846"/>
+    <n v="111345"/>
+    <n v="1064"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <s v="ROTATIVO"/>
+    <n v="3696"/>
+    <n v="27720"/>
+    <n v="56"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <s v="ROTATIVO"/>
+    <n v="3216"/>
+    <n v="24120"/>
+    <n v="362"/>
+  </r>
+  <r>
+    <x v="3"/>
+    <s v="ROTATIVO"/>
+    <n v="3112"/>
+    <n v="23340"/>
+    <n v="256"/>
+  </r>
+  <r>
+    <x v="4"/>
+    <s v="ROTATIVO"/>
+    <n v="2892"/>
+    <n v="21690"/>
+    <n v="348"/>
+  </r>
+  <r>
+    <x v="5"/>
+    <s v="ROTATIVO"/>
+    <n v="2660"/>
+    <n v="19950"/>
+    <n v="248"/>
+  </r>
+  <r>
+    <x v="6"/>
+    <s v="ROTATIVO"/>
+    <n v="2592"/>
+    <n v="19440"/>
+    <n v="128"/>
+  </r>
+  <r>
+    <x v="7"/>
+    <s v="ROTATIVO"/>
+    <n v="2552"/>
+    <n v="19140"/>
+    <n v="244"/>
+  </r>
+  <r>
+    <x v="8"/>
+    <s v="ROTATIVO"/>
+    <n v="1926"/>
+    <n v="14445"/>
+    <n v="182"/>
+  </r>
+  <r>
+    <x v="9"/>
+    <s v="ROTATIVO"/>
+    <n v="1466"/>
+    <n v="10995"/>
+    <n v="182"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <s v="ROTATIVO"/>
+    <n v="966"/>
+    <n v="7275"/>
+    <n v="120"/>
+  </r>
+  <r>
+    <x v="11"/>
+    <s v="ROTATIVO"/>
+    <n v="904"/>
+    <n v="6780"/>
+    <n v="128"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <s v="ROTATIVO"/>
+    <n v="672"/>
+    <n v="5040"/>
+    <n v="56"/>
+  </r>
+  <r>
+    <x v="13"/>
+    <s v="ROTATIVO"/>
+    <n v="672"/>
+    <n v="5040"/>
+    <n v="56"/>
+  </r>
+  <r>
+    <x v="14"/>
+    <s v="ROTATIVO"/>
+    <n v="540"/>
+    <n v="4050"/>
+    <n v="64"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <s v="ROTATIVO"/>
+    <n v="540"/>
+    <n v="4050"/>
+    <n v="64"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <s v="ROTATIVO"/>
+    <n v="540"/>
+    <n v="4050"/>
+    <n v="54"/>
+  </r>
+  <r>
+    <x v="17"/>
+    <s v="ROTATIVO"/>
+    <n v="476"/>
+    <n v="3570"/>
+    <n v="64"/>
+  </r>
+  <r>
+    <x v="18"/>
+    <s v="ROTATIVO"/>
+    <n v="436"/>
+    <n v="3270"/>
+    <n v="64"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <s v="ROTATIVO"/>
+    <n v="432"/>
+    <n v="3240"/>
+    <n v="54"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{082843A1-BA85-4CB6-8CEE-407B15854DC5}" name="Tabela dinâmica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" showAll="0" sortType="ascending">
+      <items count="26">
+        <item h="1" x="18"/>
+        <item h="1" x="8"/>
+        <item h="1" x="3"/>
+        <item h="1" x="15"/>
+        <item h="1" x="6"/>
+        <item h="1" x="11"/>
+        <item h="1" m="1" x="22"/>
+        <item h="1" x="12"/>
+        <item h="1" x="0"/>
+        <item h="1" x="16"/>
+        <item h="1" m="1" x="21"/>
+        <item h="1" x="7"/>
+        <item h="1" x="14"/>
+        <item h="1" x="10"/>
+        <item h="1" m="1" x="24"/>
+        <item h="1" m="1" x="20"/>
+        <item h="1" x="2"/>
+        <item h="1" m="1" x="23"/>
+        <item h="1" x="13"/>
+        <item h="1" x="5"/>
+        <item h="1" x="17"/>
+        <item h="1" x="4"/>
+        <item x="9"/>
+        <item h="1" x="1"/>
+        <item h="1" x="19"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="22"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Total de Vagas Rotativas" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="2" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B804E84B-8A36-4AA5-AE2C-3B5E5F71F493}" name="Tabela dinâmica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
+  <location ref="A3:C5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="5">
+    <pivotField axis="axisRow" showAll="0">
+      <items count="26">
+        <item h="1" x="18"/>
+        <item h="1" x="8"/>
+        <item h="1" x="3"/>
+        <item h="1" x="15"/>
+        <item h="1" x="6"/>
+        <item h="1" x="11"/>
+        <item h="1" x="12"/>
+        <item h="1" x="0"/>
+        <item h="1" x="16"/>
+        <item h="1" x="7"/>
+        <item h="1" x="14"/>
+        <item h="1" x="10"/>
+        <item h="1" x="2"/>
+        <item h="1" x="13"/>
+        <item h="1" x="5"/>
+        <item h="1" x="17"/>
+        <item h="1" x="4"/>
+        <item x="9"/>
+        <item h="1" x="1"/>
+        <item h="1" x="19"/>
+        <item h="1" m="1" x="20"/>
+        <item h="1" m="1" x="21"/>
+        <item h="1" m="1" x="22"/>
+        <item h="1" m="1" x="23"/>
+        <item h="1" m="1" x="24"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="0"/>
+  </rowFields>
+  <rowItems count="2">
+    <i>
+      <x v="17"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="2">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+  </colItems>
+  <dataFields count="2">
+    <dataField name="Soma de TOTAL_REGISTROS" fld="4" baseField="0" baseItem="0"/>
+    <dataField name="Soma de TOTAL_VAGAS_ROTATIVAS" fld="3" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="2">
+    <chartFormat chart="3" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="3" format="7" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãodeDados_BAIRRO" xr10:uid="{ACD14E19-B8E6-470C-8692-04A3767936D7}" sourceName="BAIRRO">
+  <pivotTables>
+    <pivotTable tabId="2" name="Tabela dinâmica1"/>
+    <pivotTable tabId="3" name="Tabela dinâmica2"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="262922932">
+      <items count="25">
+        <i x="18"/>
+        <i x="8"/>
+        <i x="3"/>
+        <i x="15"/>
+        <i x="6"/>
+        <i x="11"/>
+        <i x="12"/>
+        <i x="0"/>
+        <i x="16"/>
+        <i x="7"/>
+        <i x="14"/>
+        <i x="10"/>
+        <i x="2"/>
+        <i x="13"/>
+        <i x="5"/>
+        <i x="17"/>
+        <i x="4"/>
+        <i x="9" s="1"/>
+        <i x="1"/>
+        <i x="19"/>
+        <i x="22" nd="1"/>
+        <i x="21" nd="1"/>
+        <i x="24" nd="1"/>
+        <i x="20" nd="1"/>
+        <i x="23" nd="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="BAIRRO" xr10:uid="{00ED21F8-2472-4CBD-9030-778B45361749}" cache="SegmentaçãodeDados_BAIRRO" caption="BAIRRO" startItem="8" rowHeight="241300"/>
+</slicers>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{79E86DA9-2505-4D75-8149-8A07943A8806}" name="tb_estacionamento" displayName="tb_estacionamento" ref="A1:F21" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="A1:F21" xr:uid="{79E86DA9-2505-4D75-8149-8A07943A8806}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{FBFD7E95-B27B-4BFC-8098-48A863A50050}" name="BAIRRO" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{93C8DA85-0A28-475E-95C5-8248B8C143C6}" name="TIPO_ESTACIONAMENTO" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{B3360345-652F-4543-B6CE-5BA4B97DAD04}" name="TOTAL_VAGAS_FISICAS" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{AD79F6AA-EF08-47B2-ABBF-90A33B53417A}" name="TOTAL_VAGAS_ROTATIVAS" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{387C764D-6495-4AA6-A445-6954A46A837D}" name="TOTAL_REGISTROS" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{F770CDA2-371E-468E-8C09-ABF99A7D76D6}" name="soma_vagas_ficica+rotativa" dataDxfId="0">
+      <calculatedColumnFormula>C2+D2</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -477,17 +3810,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95BBF74A-7B43-46BE-8CF6-3F293FD0ED7B}">
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.28515625" customWidth="1"/>
-    <col min="2" max="2" width="23.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.140625" customWidth="1"/>
+    <col min="3" max="3" width="23.5703125" customWidth="1"/>
+    <col min="4" max="4" width="27" customWidth="1"/>
+    <col min="5" max="5" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="30.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -503,8 +3837,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -520,8 +3857,12 @@
       <c r="E2" s="1">
         <v>1064</v>
       </c>
+      <c r="F2" s="1">
+        <f t="shared" ref="F2:F21" si="0">C2+D2</f>
+        <v>126191</v>
+      </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -537,10 +3878,14 @@
       <c r="E3" s="1">
         <v>56</v>
       </c>
+      <c r="F3" s="1">
+        <f t="shared" si="0"/>
+        <v>31416</v>
+      </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>27</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>6</v>
@@ -554,10 +3899,14 @@
       <c r="E4" s="1">
         <v>362</v>
       </c>
+      <c r="F4" s="1">
+        <f t="shared" si="0"/>
+        <v>27336</v>
+      </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
@@ -571,10 +3920,14 @@
       <c r="E5" s="1">
         <v>256</v>
       </c>
+      <c r="F5" s="1">
+        <f t="shared" si="0"/>
+        <v>26452</v>
+      </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>6</v>
@@ -588,10 +3941,14 @@
       <c r="E6" s="1">
         <v>348</v>
       </c>
+      <c r="F6" s="1">
+        <f t="shared" si="0"/>
+        <v>24582</v>
+      </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>6</v>
@@ -605,10 +3962,14 @@
       <c r="E7" s="1">
         <v>248</v>
       </c>
+      <c r="F7" s="1">
+        <f t="shared" si="0"/>
+        <v>22610</v>
+      </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>6</v>
@@ -622,10 +3983,14 @@
       <c r="E8" s="1">
         <v>128</v>
       </c>
+      <c r="F8" s="1">
+        <f t="shared" si="0"/>
+        <v>22032</v>
+      </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>13</v>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>6</v>
@@ -639,10 +4004,14 @@
       <c r="E9" s="1">
         <v>244</v>
       </c>
+      <c r="F9" s="1">
+        <f t="shared" si="0"/>
+        <v>21692</v>
+      </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>6</v>
@@ -656,10 +4025,14 @@
       <c r="E10" s="1">
         <v>182</v>
       </c>
+      <c r="F10" s="1">
+        <f t="shared" si="0"/>
+        <v>16371</v>
+      </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>6</v>
@@ -673,10 +4046,14 @@
       <c r="E11" s="1">
         <v>182</v>
       </c>
+      <c r="F11" s="1">
+        <f t="shared" si="0"/>
+        <v>12461</v>
+      </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>6</v>
@@ -690,10 +4067,14 @@
       <c r="E12" s="1">
         <v>120</v>
       </c>
+      <c r="F12" s="1">
+        <f t="shared" si="0"/>
+        <v>8241</v>
+      </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>6</v>
@@ -707,10 +4088,14 @@
       <c r="E13" s="1">
         <v>128</v>
       </c>
+      <c r="F13" s="1">
+        <f t="shared" si="0"/>
+        <v>7684</v>
+      </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>18</v>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>24</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>6</v>
@@ -724,10 +4109,14 @@
       <c r="E14" s="1">
         <v>56</v>
       </c>
+      <c r="F14" s="1">
+        <f t="shared" si="0"/>
+        <v>5712</v>
+      </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>19</v>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>28</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>6</v>
@@ -741,10 +4130,14 @@
       <c r="E15" s="1">
         <v>56</v>
       </c>
+      <c r="F15" s="1">
+        <f t="shared" si="0"/>
+        <v>5712</v>
+      </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>6</v>
@@ -758,10 +4151,14 @@
       <c r="E16" s="1">
         <v>64</v>
       </c>
+      <c r="F16" s="1">
+        <f t="shared" si="0"/>
+        <v>4590</v>
+      </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>6</v>
@@ -775,10 +4172,14 @@
       <c r="E17" s="1">
         <v>64</v>
       </c>
+      <c r="F17" s="1">
+        <f t="shared" si="0"/>
+        <v>4590</v>
+      </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>6</v>
@@ -792,10 +4193,14 @@
       <c r="E18" s="1">
         <v>54</v>
       </c>
+      <c r="F18" s="1">
+        <f t="shared" si="0"/>
+        <v>4590</v>
+      </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>23</v>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>6</v>
@@ -809,10 +4214,14 @@
       <c r="E19" s="1">
         <v>64</v>
       </c>
+      <c r="F19" s="1">
+        <f t="shared" si="0"/>
+        <v>4046</v>
+      </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>6</v>
@@ -826,10 +4235,14 @@
       <c r="E20" s="1">
         <v>64</v>
       </c>
+      <c r="F20" s="1">
+        <f t="shared" si="0"/>
+        <v>3706</v>
+      </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>6</v>
@@ -842,9 +4255,140 @@
       </c>
       <c r="E21" s="1">
         <v>54</v>
+      </c>
+      <c r="F21" s="1">
+        <f t="shared" si="0"/>
+        <v>3672</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDB411EF-6C70-4274-977F-100924232B2A}">
+  <dimension ref="A3:C24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="4">
+        <v>10995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="4">
+        <v>10995</v>
+      </c>
+    </row>
+    <row r="24" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C24">
+        <f>B24</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C2C1461-B5A0-42B4-9650-F4DFF90CE05E}">
+  <dimension ref="A3:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="4">
+        <v>182</v>
+      </c>
+      <c r="C4" s="4">
+        <v>10995</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="4">
+        <v>182</v>
+      </c>
+      <c r="C5" s="4">
+        <v>10995</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38AB2DC6-0379-4025-84C9-7EB8BAD8C0A9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="5"/>
+  </cols>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId2"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE9427C0-2F8C-495D-AD29-9DFBF974106B}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/data/estacionamento_bh.xlsx
+++ b/data/estacionamento_bh.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patrick\Desktop\Curso em Vídeo HTML5 e CSS3\exercicios\dashboard-estacionamento-bh\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57A68FFA-532A-414E-810D-5C9128DDABBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{252BB3A5-FE8D-4BE2-9897-B8C29D66BE4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="3" xr2:uid="{8316B71B-52D7-42FF-8630-4572AF6B553D}"/>
   </bookViews>
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="181029"/>
   <pivotCaches>
-    <pivotCache cacheId="1" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -190,8 +190,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -338,49 +338,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -546,7 +504,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>SERRA</c:v>
+                  <c:v>BARRO PRETO</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -558,7 +516,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>10995</c:v>
+                  <c:v>23340</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -946,49 +904,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="diamond"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent1">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1020,7 +936,6 @@
               <a:endParaRPr lang="pt-BR"/>
             </a:p>
           </c:txPr>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -1073,49 +988,7 @@
           </a:effectLst>
         </c:spPr>
         <c:marker>
-          <c:symbol val="square"/>
-          <c:size val="5"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent2">
-                    <a:satMod val="103000"/>
-                    <a:lumMod val="102000"/>
-                    <a:tint val="94000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="50000">
-                  <a:schemeClr val="accent2">
-                    <a:satMod val="110000"/>
-                    <a:lumMod val="100000"/>
-                    <a:shade val="100000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="99000"/>
-                    <a:satMod val="120000"/>
-                    <a:shade val="78000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="5400000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="63000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1147,7 +1020,6 @@
               <a:endParaRPr lang="pt-BR"/>
             </a:p>
           </c:txPr>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -1250,7 +1122,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>SERRA</c:v>
+                  <c:v>BARRO PRETO</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1262,7 +1134,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>182</c:v>
+                  <c:v>256</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1332,7 +1204,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>SERRA</c:v>
+                  <c:v>BARRO PRETO</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1344,7 +1216,7 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>10995</c:v>
+                  <c:v>23340</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1356,7 +1228,6 @@
           </c:extLst>
         </c:ser>
         <c:dLbls>
-          <c:dLblPos val="outEnd"/>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
           <c:showCatName val="0"/>
@@ -2754,8 +2625,8 @@
       <xdr:row>21</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="7" name="BAIRRO">
@@ -2778,7 +2649,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -3275,14 +3146,14 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{082843A1-BA85-4CB6-8CEE-407B15854DC5}" name="Tabela dinâmica1" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{082843A1-BA85-4CB6-8CEE-407B15854DC5}" name="Tabela dinâmica1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="A3:B5" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0" sortType="ascending">
       <items count="26">
         <item h="1" x="18"/>
         <item h="1" x="8"/>
-        <item h="1" x="3"/>
+        <item x="3"/>
         <item h="1" x="15"/>
         <item h="1" x="6"/>
         <item h="1" x="11"/>
@@ -3302,7 +3173,7 @@
         <item h="1" x="5"/>
         <item h="1" x="17"/>
         <item h="1" x="4"/>
-        <item x="9"/>
+        <item h="1" x="9"/>
         <item h="1" x="1"/>
         <item h="1" x="19"/>
         <item t="default"/>
@@ -3318,7 +3189,7 @@
   </rowFields>
   <rowItems count="2">
     <i>
-      <x v="22"/>
+      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
@@ -3354,14 +3225,14 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B804E84B-8A36-4AA5-AE2C-3B5E5F71F493}" name="Tabela dinâmica2" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{B804E84B-8A36-4AA5-AE2C-3B5E5F71F493}" name="Tabela dinâmica2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="12">
   <location ref="A3:C5" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="5">
     <pivotField axis="axisRow" showAll="0">
       <items count="26">
         <item h="1" x="18"/>
         <item h="1" x="8"/>
-        <item h="1" x="3"/>
+        <item x="3"/>
         <item h="1" x="15"/>
         <item h="1" x="6"/>
         <item h="1" x="11"/>
@@ -3376,7 +3247,7 @@
         <item h="1" x="5"/>
         <item h="1" x="17"/>
         <item h="1" x="4"/>
-        <item x="9"/>
+        <item h="1" x="9"/>
         <item h="1" x="1"/>
         <item h="1" x="19"/>
         <item h="1" m="1" x="20"/>
@@ -3397,7 +3268,7 @@
   </rowFields>
   <rowItems count="2">
     <i>
-      <x v="17"/>
+      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
@@ -3461,7 +3332,7 @@
       <items count="25">
         <i x="18"/>
         <i x="8"/>
-        <i x="3"/>
+        <i x="3" s="1"/>
         <i x="15"/>
         <i x="6"/>
         <i x="11"/>
@@ -3476,7 +3347,7 @@
         <i x="5"/>
         <i x="17"/>
         <i x="4"/>
-        <i x="9" s="1"/>
+        <i x="9"/>
         <i x="1"/>
         <i x="19"/>
         <i x="22" nd="1"/>
@@ -3492,7 +3363,7 @@
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
 <slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="BAIRRO" xr10:uid="{00ED21F8-2472-4CBD-9030-778B45361749}" cache="SegmentaçãodeDados_BAIRRO" caption="BAIRRO" startItem="8" rowHeight="241300"/>
+  <slicer name="BAIRRO" xr10:uid="{00ED21F8-2472-4CBD-9030-778B45361749}" cache="SegmentaçãodeDados_BAIRRO" caption="BAIRRO" rowHeight="241300"/>
 </slicers>
 </file>
 
@@ -4288,18 +4159,18 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="4">
-        <v>10995</v>
+        <v>8</v>
+      </c>
+      <c r="B4" s="5">
+        <v>23340</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="4">
-        <v>10995</v>
+      <c r="B5" s="5">
+        <v>23340</v>
       </c>
     </row>
     <row r="24" spans="3:3" x14ac:dyDescent="0.25">
@@ -4338,24 +4209,24 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="4">
-        <v>182</v>
-      </c>
-      <c r="C4" s="4">
-        <v>10995</v>
+        <v>8</v>
+      </c>
+      <c r="B4" s="5">
+        <v>256</v>
+      </c>
+      <c r="C4" s="5">
+        <v>23340</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="4">
-        <v>182</v>
-      </c>
-      <c r="C5" s="4">
-        <v>10995</v>
+      <c r="B5" s="5">
+        <v>256</v>
+      </c>
+      <c r="C5" s="5">
+        <v>23340</v>
       </c>
     </row>
   </sheetData>
@@ -4368,7 +4239,7 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
